--- a/Donné/Book1.xlsx
+++ b/Donné/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage Lucas Chabert\Valeur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage_Lucas_Chabert\Donné\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9AEF57B-E1BF-4CC1-8E44-2433CC2CA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A47D1B-C945-424C-B7FA-D90B816E10DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EEEFC58F-7EA2-451A-9A53-CFDF5F211B26}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Tour</t>
   </si>
@@ -129,12 +129,15 @@
   <si>
     <t>C1(3)</t>
   </si>
+  <si>
+    <t>=</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,24 +503,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB04403-9123-4789-897E-4074D25BBD8D}">
-  <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:W35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.796875" style="1"/>
-    <col min="4" max="4" width="18.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.09765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.77734375" style="1"/>
+    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.796875" style="1"/>
+    <col min="9" max="11" width="8.77734375" style="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="14" max="14" width="19.296875" customWidth="1"/>
-    <col min="20" max="20" width="22.796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.796875" customWidth="1"/>
-    <col min="22" max="22" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" customWidth="1"/>
+    <col min="20" max="20" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.77734375" customWidth="1"/>
+    <col min="22" max="22" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,16 +582,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <f>A2 * 4</f>
+        <f t="shared" ref="B2:B32" si="0">A2 * 4</f>
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <f xml:space="preserve"> 6 - B2</f>
+        <f t="shared" ref="C2:C32" si="1" xml:space="preserve"> 6 - B2</f>
         <v>6</v>
       </c>
       <c r="D2" s="1">
@@ -645,17 +648,17 @@
         <v>1.167</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>1/8+A2</f>
         <v>0.125</v>
       </c>
       <c r="B3" s="1">
-        <f>A3 * 4</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="C3" s="1">
-        <f xml:space="preserve"> 6 - B3</f>
+        <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
       <c r="D3" s="1">
@@ -671,19 +674,19 @@
         <v>0.23</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L32" si="0">$O$2*F3+$P$2</f>
+        <f t="shared" ref="L3:L32" si="2">$O$2*F3+$P$2</f>
         <v>3.8817867550836134</v>
       </c>
       <c r="M3" s="1">
-        <f t="shared" ref="M3:M32" si="1">(L3-C3)^2</f>
+        <f t="shared" ref="M3:M32" si="3">(L3-C3)^2</f>
         <v>2.6186141060228216</v>
       </c>
       <c r="R3" s="1">
-        <f t="shared" ref="R3:R32" si="2" xml:space="preserve">  D3 - $D$2</f>
+        <f t="shared" ref="R3:R32" si="4" xml:space="preserve">  D3 - $D$2</f>
         <v>1.0000000000000231E-2</v>
       </c>
       <c r="S3" s="1">
-        <f t="shared" ref="S3:S32" si="3">G3-$G$2</f>
+        <f t="shared" ref="S3:S31" si="5">G3-$G$2</f>
         <v>0</v>
       </c>
       <c r="T3">
@@ -699,17 +702,17 @@
         <v>1.167</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A17" si="4">1/8+A3</f>
+        <f t="shared" ref="A4:A17" si="6">1/8+A3</f>
         <v>0.25</v>
       </c>
       <c r="B4" s="1">
-        <f>A4 * 4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <f xml:space="preserve"> 6 - B4</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="D4" s="1">
@@ -725,19 +728,19 @@
         <v>0.24</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8563175129201341</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3080096312531875</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8000000000000238E-2</v>
       </c>
       <c r="S4" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
       <c r="T4">
@@ -753,17 +756,17 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.375</v>
       </c>
       <c r="B5" s="1">
-        <f>A5 * 4</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="C5" s="1">
-        <f xml:space="preserve"> 6 - B5</f>
+        <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
       <c r="D5" s="1">
@@ -779,19 +782,19 @@
         <v>0.25</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8308482707566549</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.447764036749359</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.8000000000000256E-2</v>
       </c>
       <c r="S5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7.0000000000000062E-3</v>
       </c>
       <c r="T5">
@@ -807,17 +810,17 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="B6" s="1">
-        <f>A6 * 4</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <f xml:space="preserve"> 6 - B6</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="D6" s="1">
@@ -833,19 +836,19 @@
         <v>0.25700000000000001</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8053790285931757</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.787732251133593E-2</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.0000000000000266E-2</v>
       </c>
       <c r="S6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8.0000000000000071E-3</v>
       </c>
       <c r="T6">
@@ -861,17 +864,17 @@
         <v>1.1890000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.625</v>
       </c>
       <c r="B7" s="1">
-        <f>A7 * 4</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="C7" s="1">
-        <f xml:space="preserve"> 6 - B7</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
       <c r="D7" s="1">
@@ -887,19 +890,19 @@
         <v>0.26100000000000001</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.6780328177757804</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.1695684205184226E-2</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.4000000000000012E-2</v>
       </c>
       <c r="T7">
@@ -915,17 +918,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
       <c r="B8" s="1">
-        <f>A8 * 4</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <f xml:space="preserve"> 6 - B8</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="D8" s="1">
@@ -941,19 +944,19 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.6627512724776929</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.4392392491708012</v>
       </c>
       <c r="R8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="S8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.4000000000000021E-2</v>
       </c>
       <c r="T8">
@@ -969,17 +972,17 @@
         <v>1.244</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.875</v>
       </c>
       <c r="B9" s="1">
-        <f>A9 * 4</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="C9" s="1">
-        <f xml:space="preserve"> 6 - B9</f>
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
       <c r="D9" s="1">
@@ -995,19 +998,19 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.4462627140881192</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.89541312407341367</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.11100000000000021</v>
       </c>
       <c r="S9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.8999999999999979E-2</v>
       </c>
       <c r="T9">
@@ -1023,17 +1026,17 @@
         <v>1.3009999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="B10" s="1">
-        <f>A10 * 4</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C10" s="1">
-        <f xml:space="preserve"> 6 - B10</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D10" s="1">
@@ -1049,19 +1052,19 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.2959941853235919</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.6796009283925606</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1379999999999999</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4.6999999999999986E-2</v>
       </c>
       <c r="T10">
@@ -1077,17 +1080,17 @@
         <v>1.373</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.125</v>
       </c>
       <c r="B11" s="1">
-        <f>A11 * 4</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="C11" s="1">
-        <f xml:space="preserve"> 6 - B11</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="D11" s="1">
@@ -1103,19 +1106,19 @@
         <v>0.3</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.0413017636888005</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.3756111267502069</v>
       </c>
       <c r="R11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="S11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="T11">
@@ -1131,17 +1134,17 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.25</v>
       </c>
       <c r="B12" s="1">
-        <f>A12 * 4</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <f xml:space="preserve"> 6 - B12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D12" s="1">
@@ -1157,19 +1160,19 @@
         <v>0.32</v>
       </c>
       <c r="L12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.6592631312366124</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.7531541386811278</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.20000000000000018</v>
       </c>
       <c r="S12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7.7000000000000013E-2</v>
       </c>
       <c r="T12">
@@ -1185,17 +1188,17 @@
         <v>1.597</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.375</v>
       </c>
       <c r="B13" s="1">
-        <f>A13 * 4</f>
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
       <c r="C13" s="1">
-        <f xml:space="preserve"> 6 - B13</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="D13" s="1">
@@ -1211,19 +1214,19 @@
         <v>0.34</v>
       </c>
       <c r="L13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.9333897295774554</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.0546061168581304</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.24000000000000021</v>
       </c>
       <c r="S13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9.7999999999999976E-2</v>
       </c>
       <c r="T13">
@@ -1239,17 +1242,17 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="B14" s="1">
-        <f>A14 * 4</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C14" s="1">
-        <f xml:space="preserve"> 6 - B14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D14" s="1">
@@ -1265,19 +1268,19 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.4876779917165699</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.2131858070378465</v>
       </c>
       <c r="R14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.41999999999999993</v>
       </c>
       <c r="S14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.11399999999999999</v>
       </c>
       <c r="T14">
@@ -1293,17 +1296,17 @@
         <v>1.9570000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.625</v>
       </c>
       <c r="B15" s="1">
-        <f>A15 * 4</f>
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
       <c r="C15" s="1">
-        <f xml:space="preserve"> 6 - B15</f>
+        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
       <c r="D15" s="1">
@@ -1319,19 +1322,19 @@
         <v>0.372</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.93244851255272287</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.0519087411145081</v>
       </c>
       <c r="R15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45000000000000018</v>
       </c>
       <c r="S15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.13900000000000001</v>
       </c>
       <c r="T15">
@@ -1347,17 +1350,17 @@
         <v>2.1459999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.75</v>
       </c>
       <c r="B16" s="1">
-        <f>A16 * 4</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1">
-        <f xml:space="preserve"> 6 - B16</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="D16" s="1">
@@ -1373,19 +1376,19 @@
         <v>0.40200000000000002</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.2136673848038404</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.61831898172123156</v>
       </c>
       <c r="R16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.55000000000000027</v>
       </c>
       <c r="S16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.17099999999999999</v>
       </c>
       <c r="T16">
@@ -1401,17 +1404,17 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.875</v>
       </c>
       <c r="B17" s="1">
-        <f>A17 * 4</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="C17" s="1">
-        <f xml:space="preserve"> 6 - B17</f>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="D17" s="1">
@@ -1427,19 +1430,19 @@
         <v>0.46</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.7427631316373233</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.544460201357007</v>
       </c>
       <c r="R17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.94</v>
       </c>
       <c r="S17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.21300000000000002</v>
       </c>
       <c r="T17">
@@ -1455,16 +1458,16 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1.75</v>
       </c>
       <c r="B18" s="1">
-        <f>A18 * 4</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C18" s="1">
-        <f xml:space="preserve"> 6 - B18</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="D18" s="1">
@@ -1480,19 +1483,19 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.8930316604018511</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.5835688672837893</v>
       </c>
       <c r="R18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="S18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.21700000000000003</v>
       </c>
       <c r="T18">
@@ -1508,17 +1511,17 @@
         <v>3.0819999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f xml:space="preserve"> A18 - 1/8</f>
         <v>1.625</v>
       </c>
       <c r="B19" s="1">
-        <f>A19 * 4</f>
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
       <c r="C19" s="1">
-        <f xml:space="preserve"> 6 - B19</f>
+        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
       <c r="D19" s="1">
@@ -1534,19 +1537,19 @@
         <v>0.42</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.1101847089583075</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.3723253790465344</v>
       </c>
       <c r="R19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="S19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.193</v>
       </c>
       <c r="T19">
@@ -1562,17 +1565,17 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A32" si="5" xml:space="preserve"> A19 - 1/8</f>
+        <f t="shared" ref="A20:A32" si="7" xml:space="preserve"> A19 - 1/8</f>
         <v>1.5</v>
       </c>
       <c r="B20" s="1">
-        <f>A20 * 4</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C20" s="1">
-        <f xml:space="preserve"> 6 - B20</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D20" s="1">
@@ -1588,19 +1591,19 @@
         <v>0.39400000000000002</v>
       </c>
       <c r="L20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.1400430561735497E-2</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.7700128731665023E-3</v>
       </c>
       <c r="R20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.55000000000000027</v>
       </c>
       <c r="S20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.16299999999999998</v>
       </c>
       <c r="T20">
@@ -1616,17 +1619,17 @@
         <v>2.5760000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.375</v>
       </c>
       <c r="B21" s="1">
-        <f>A21 * 4</f>
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
       <c r="C21" s="1">
-        <f xml:space="preserve"> 6 - B21</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="D21" s="1">
@@ -1642,19 +1645,19 @@
         <v>0.37</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.92735466412002765</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.18263200894514164</v>
       </c>
       <c r="R21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45000000000000018</v>
       </c>
       <c r="S21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="T21">
@@ -1670,17 +1673,17 @@
         <v>2.2469999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
       <c r="B22" s="1">
-        <f>A22 * 4</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C22" s="1">
-        <f xml:space="preserve"> 6 - B22</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D22" s="1">
@@ -1696,19 +1699,19 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="L22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.8136842914091034</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.66208212608593464</v>
       </c>
       <c r="R22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="S22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.11299999999999999</v>
       </c>
       <c r="T22">
@@ -1724,17 +1727,17 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.125</v>
       </c>
       <c r="B23" s="1">
-        <f>A23 * 4</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="C23" s="1">
-        <f xml:space="preserve"> 6 - B23</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="D23" s="1">
@@ -1750,19 +1753,19 @@
         <v>0.32</v>
       </c>
       <c r="L23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.4631499665778227</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.92765785811886103</v>
       </c>
       <c r="R23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.18999999999999995</v>
       </c>
       <c r="S23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8.3000000000000018E-2</v>
       </c>
       <c r="T23">
@@ -1778,17 +1781,17 @@
         <v>1.6990000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="B24" s="1">
-        <f>A24 * 4</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C24" s="1">
-        <f xml:space="preserve"> 6 - B24</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D24" s="1">
@@ -1804,19 +1807,19 @@
         <v>0.311</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.8273601295155752</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.68452478391202942</v>
       </c>
       <c r="R24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="S24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.3E-2</v>
       </c>
       <c r="T24">
@@ -1832,17 +1835,17 @@
         <v>1.5629999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.875</v>
       </c>
       <c r="B25" s="1">
-        <f>A25 * 4</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="C25" s="1">
-        <f xml:space="preserve"> 6 - B25</f>
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
       <c r="D25" s="1">
@@ -1858,19 +1861,19 @@
         <v>0.3</v>
       </c>
       <c r="L25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.0922402480157589</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.35074851136976765</v>
       </c>
       <c r="R25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="S25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.2E-2</v>
       </c>
       <c r="T25">
@@ -1886,17 +1889,17 @@
         <v>1.4770000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="B26" s="1">
-        <f>A26 * 4</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C26" s="1">
-        <f xml:space="preserve"> 6 - B26</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="D26" s="1">
@@ -1912,19 +1915,19 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.3724019118140296</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.13868318392274429</v>
       </c>
       <c r="R26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.10999999999999988</v>
       </c>
       <c r="S26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4.3999999999999984E-2</v>
       </c>
       <c r="T26">
@@ -1940,17 +1943,17 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.625</v>
       </c>
       <c r="B27" s="1">
-        <f>A27 * 4</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="C27" s="1">
-        <f xml:space="preserve"> 6 - B27</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
       <c r="D27" s="1">
@@ -1966,19 +1969,19 @@
         <v>0.28100000000000003</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.5812496975545591</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.6015133527073319E-3</v>
       </c>
       <c r="R27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="S27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.7999999999999969E-2</v>
       </c>
       <c r="T27">
@@ -1994,17 +1997,17 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="B28" s="1">
-        <f>A28 * 4</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C28" s="1">
-        <f xml:space="preserve"> 6 - B28</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="D28" s="1">
@@ -2020,19 +2023,19 @@
         <v>0.26</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.6933143630738678</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.4056079896787353E-2</v>
       </c>
       <c r="R28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.899999999999995E-2</v>
       </c>
       <c r="S28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.1000000000000019E-2</v>
       </c>
       <c r="T28">
@@ -2048,17 +2051,17 @@
         <v>1.2270000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.375</v>
       </c>
       <c r="B29" s="1">
-        <f>A29 * 4</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="C29" s="1">
-        <f xml:space="preserve"> 6 - B29</f>
+        <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
       <c r="D29" s="1">
@@ -2074,19 +2077,19 @@
         <v>0.26</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.7417059231844783</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.5750099069335044</v>
       </c>
       <c r="R29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.0000000000000266E-2</v>
       </c>
       <c r="S29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.3000000000000012E-2</v>
       </c>
       <c r="T29">
@@ -2102,17 +2105,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
       <c r="B30" s="1">
-        <f>A30 * 4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C30" s="1">
-        <f xml:space="preserve"> 6 - B30</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="D30" s="1">
@@ -2128,19 +2131,19 @@
         <v>0.253</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8053790285931757</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.4271192653249847</v>
       </c>
       <c r="R30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.0000000000000249E-2</v>
       </c>
       <c r="S30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8.0000000000000071E-3</v>
       </c>
       <c r="T30">
@@ -2156,17 +2159,17 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
       <c r="B31" s="1">
-        <f>A31 * 4</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="C31" s="1">
-        <f xml:space="preserve"> 6 - B31</f>
+        <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
       <c r="D31" s="1">
@@ -2182,19 +2185,19 @@
         <v>0.246</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8308482707566549</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.7860674952360491</v>
       </c>
       <c r="R31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0000000000000231E-2</v>
       </c>
       <c r="S31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0000000000000018E-3</v>
       </c>
       <c r="T31">
@@ -2210,17 +2213,17 @@
         <v>1.1830000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="B32" s="1">
-        <f>A32 * 4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <f xml:space="preserve"> 6 - B32</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="D32" s="1">
@@ -2233,15 +2236,15 @@
         <v>0.24</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.8563175129201341</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.5953746054129194</v>
       </c>
       <c r="R32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1.9999999999997797E-3</v>
       </c>
       <c r="S32" s="1"/>
@@ -2256,6 +2259,11 @@
       </c>
       <c r="W32">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Donné/Book1.xlsx
+++ b/Donné/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage_Lucas_Chabert\Donné\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A47D1B-C945-424C-B7FA-D90B816E10DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4329D5-C9C9-42B1-8158-0784150789C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EEEFC58F-7EA2-451A-9A53-CFDF5F211B26}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Tour</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>C1(3)</t>
-  </si>
-  <si>
-    <t>=</t>
   </si>
 </sst>
 </file>
@@ -503,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB04403-9123-4789-897E-4074D25BBD8D}">
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.77734375" style="1"/>
@@ -2147,10 +2144,10 @@
         <v>8.0000000000000071E-3</v>
       </c>
       <c r="T30">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="U30">
         <v>1.1850000000000001</v>
-      </c>
-      <c r="U30">
-        <v>0.17499999999999999</v>
       </c>
       <c r="V30">
         <v>0.17499999999999999</v>
@@ -2261,11 +2258,6 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Donné/Book1.xlsx
+++ b/Donné/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Stage_Lucas_Chabert\Donné\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4329D5-C9C9-42B1-8158-0784150789C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D41D72-B3A4-4CC8-9650-4320D5CBB368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EEEFC58F-7EA2-451A-9A53-CFDF5F211B26}"/>
+    <workbookView xWindow="2268" yWindow="2328" windowWidth="17280" windowHeight="8976" xr2:uid="{EEEFC58F-7EA2-451A-9A53-CFDF5F211B26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Tour</t>
   </si>
@@ -129,6 +129,42 @@
   <si>
     <t>C1(3)</t>
   </si>
+  <si>
+    <t>deltad/sE2</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>1/C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b = </t>
+  </si>
+  <si>
+    <t>1/C2 - 1/C1</t>
+  </si>
+  <si>
+    <t>reconstruit</t>
+  </si>
+  <si>
+    <t>a moy</t>
+  </si>
+  <si>
+    <t>b moy</t>
+  </si>
+  <si>
+    <t>erreur</t>
+  </si>
+  <si>
+    <t>C2 (4)</t>
+  </si>
 </sst>
 </file>
 
@@ -181,6 +217,2621 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$X$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>deltad/sE2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$X$2:$X$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>2.2976761033575803</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2976761033575803</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2899532333494594</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2389621259677757</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.235880183735524</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.1878147029204427</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.128692798747772</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0403492559742293</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0189206278062795</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.9466601075231034</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.9118969895966105</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.8478408014078789</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.809199411476679</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.7269992315364364</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6615834286440461</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5652490444700597</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.5481945426749981</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6194873853978451</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.6951345755693583</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.7431459792244264</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.8047480620155039</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.9114184814596822</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9917836818533861</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.9614743570276338</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.0347889848460161</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1048999309868881</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.1435839566364301</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.1969696969696968</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.236586942469295</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.2894877006282841</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3276-472C-BA41-321BC64CECDB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1/C2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AA$2:$AA$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>3.1545741324921135</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.1545741324921135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1446540880503142</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0864197530864197</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0769230769230766</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.0211480362537761</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9325513196480935</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.808988764044944</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.7472527472527473</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.6178010471204187</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5380710659898478</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4096385542168677</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3201856148491879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1929824561403506</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0491803278688523</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.8867924528301885</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.8726591760299625</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.9607843137254901</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.0833333333333335</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.1881838074398248</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.3255813953488373</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.6315789473684212</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.6385224274406331</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.770083102493075</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.8985507246376816</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.9585798816568047</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.0303030303030303</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.0769230769230766</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.134796238244514</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3276-472C-BA41-321BC64CECDB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1376578335"/>
+        <c:axId val="1376578815"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1376578335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1376578815"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1376578815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1376578335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AK$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>C2 (4)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AK$2:$AK$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>0.76500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.77800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.78600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.80500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.81100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.81899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.83199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.85199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.86699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.92200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.97199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.84599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.82299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.81499999999999995</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.80700000000000005</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.79900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.79700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.78800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.78300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.77200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.76900000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5CEB-4700-B234-2149651F820B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1917270591"/>
+        <c:axId val="1917271071"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1917270591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1917271071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1917271071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1917270591"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>643742</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>50469</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>310489</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>161553</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEE21E2C-96E8-DE8B-AD4F-4DF7297A6C54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>468924</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>404446</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>64476</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F67CA7BC-5D03-ABC1-7B9B-6B115935517E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,7 +3151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB04403-9123-4789-897E-4074D25BBD8D}">
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.77734375" style="1"/>
@@ -515,9 +3166,11 @@
     <col min="20" max="20" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8.77734375" customWidth="1"/>
     <col min="22" max="22" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,8 +3231,44 @@
       <c r="W1" t="s">
         <v>18</v>
       </c>
+      <c r="X1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -644,8 +3333,55 @@
       <c r="W2">
         <v>1.167</v>
       </c>
+      <c r="X2">
+        <f>AA2 - 1/W2</f>
+        <v>2.2976761033575803</v>
+      </c>
+      <c r="Y2" s="1">
+        <f>AVERAGE(F2,U2,W2)</f>
+        <v>1.1323333333333334</v>
+      </c>
+      <c r="Z2" s="1">
+        <f>AVERAGE(T2,V2,H2)</f>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="AA2">
+        <f>1/G2</f>
+        <v>3.1545741324921135</v>
+      </c>
+      <c r="AC2">
+        <f xml:space="preserve"> ((1/Z2 - 1/Y2) - (1/Z3-1/Y3) )/( C2-C3)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <f>1/Z2 - 1/Y2 - AC2 * C2</f>
+        <v>4.3800257192879162</v>
+      </c>
+      <c r="AE2">
+        <f>1/Z2 - 1/Y2</f>
+        <v>4.3800257192879162</v>
+      </c>
+      <c r="AF2">
+        <f xml:space="preserve"> AH2 * C2 +AI2</f>
+        <v>4.65258419856168</v>
+      </c>
+      <c r="AG2">
+        <f>AE2-AF2/AE2</f>
+        <v>3.3177981213828347</v>
+      </c>
+      <c r="AH2">
+        <f>AVERAGE($AC$2:$AC$31)</f>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI2">
+        <f>AVERAGE($AD$2:$AD$31)</f>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK2">
+        <v>0.76500000000000001</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f>1/8+A2</f>
         <v>0.125</v>
@@ -698,10 +3434,57 @@
       <c r="W3">
         <v>1.167</v>
       </c>
+      <c r="X3">
+        <f t="shared" ref="X3:X32" si="6">AA3 - 1/W3</f>
+        <v>2.2976761033575803</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ref="Y3:Y32" si="7">AVERAGE(F3,U3,W3)</f>
+        <v>1.1323333333333334</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ref="Z3:Z32" si="8">AVERAGE(T3,V3,H3)</f>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" ref="AA3:AA32" si="9">1/G3</f>
+        <v>3.1545741324921135</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC32" si="10" xml:space="preserve"> ((1/Z3 - 1/Y3) - (1/Z4-1/Y4) )/( C3-C4)</f>
+        <v>0.17269309665716293</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD32" si="11">1/Z3 - 1/Y3 - AC3 * C3</f>
+        <v>3.4302136876735201</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" ref="AE3:AE32" si="12">1/Z3 - 1/Y3</f>
+        <v>4.3800257192879162</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" ref="AF3:AF32" si="13" xml:space="preserve"> AH3 * C3 +AI3</f>
+        <v>4.5210637542685186</v>
+      </c>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG32" si="14">AE3-AF3/AE3</f>
+        <v>3.3478254437599606</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AH32" si="15">AVERAGE($AC$2:$AC$31)</f>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI32" si="16">AVERAGE($AD$2:$AD$31)</f>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK3">
+        <v>0.76500000000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A17" si="6">1/8+A3</f>
+        <f t="shared" ref="A4:A17" si="17">1/8+A3</f>
         <v>0.25</v>
       </c>
       <c r="B4" s="1">
@@ -752,10 +3535,57 @@
       <c r="W4">
         <v>1.17</v>
       </c>
+      <c r="X4">
+        <f t="shared" si="6"/>
+        <v>2.2899532333494594</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1379999999999999</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="8"/>
+        <v>0.19333333333333336</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="9"/>
+        <v>3.1446540880503142</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="10"/>
+        <v>0.26189881980218743</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="11"/>
+        <v>2.9841850719483975</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" si="12"/>
+        <v>4.2936791709593347</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="13"/>
+        <v>4.3895433099753571</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="14"/>
+        <v>3.271352365625483</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK4">
+        <v>0.77</v>
+      </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0.375</v>
       </c>
       <c r="B5" s="1">
@@ -806,10 +3636,57 @@
       <c r="W5">
         <v>1.18</v>
       </c>
+      <c r="X5">
+        <f t="shared" si="6"/>
+        <v>2.2389621259677757</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1483333333333334</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="8"/>
+        <v>0.19866666666666666</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="9"/>
+        <v>3.0864197530864197</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="10"/>
+        <v>0.15258002218492095</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="11"/>
+        <v>3.4761196612260967</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="12"/>
+        <v>4.162729761058241</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="13"/>
+        <v>4.2580228656821948</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="14"/>
+        <v>3.1398377862979752</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK5">
+        <v>0.77800000000000002</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0.5</v>
       </c>
       <c r="B6" s="1">
@@ -860,10 +3737,57 @@
       <c r="W6">
         <v>1.1890000000000001</v>
       </c>
+      <c r="X6">
+        <f t="shared" si="6"/>
+        <v>2.235880183735524</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1573333333333335</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20199999999999999</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="9"/>
+        <v>3.0769230769230766</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="10"/>
+        <v>4.5914490492126703E-2</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="11"/>
+        <v>3.9027817879972737</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="12"/>
+        <v>4.0864397499657805</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="13"/>
+        <v>4.1265024213890324</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="14"/>
+        <v>3.0766359417917855</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK6">
+        <v>0.78100000000000003</v>
+      </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0.625</v>
       </c>
       <c r="B7" s="1">
@@ -914,10 +3838,57 @@
       <c r="W7">
         <v>1.2</v>
       </c>
+      <c r="X7">
+        <f t="shared" si="6"/>
+        <v>2.1878147029204427</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1813333333333331</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20366666666666666</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="9"/>
+        <v>3.0211480362537761</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="10"/>
+        <v>0.39670185154469806</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="11"/>
+        <v>2.675026024313274</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="12"/>
+        <v>4.0634825047197172</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="13"/>
+        <v>3.994981977095871</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="14"/>
+        <v>3.0803400960946727</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK7">
+        <v>0.78600000000000003</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0.75</v>
       </c>
       <c r="B8" s="1">
@@ -968,10 +3939,57 @@
       <c r="W8">
         <v>1.244</v>
       </c>
+      <c r="X8">
+        <f t="shared" si="6"/>
+        <v>2.128692798747772</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" si="7"/>
+        <v>1.216</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" si="8"/>
+        <v>0.21333333333333335</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="9"/>
+        <v>2.9325513196480935</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="10"/>
+        <v>0.33040540981852828</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="11"/>
+        <v>2.8739153494917833</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="12"/>
+        <v>3.8651315789473681</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="13"/>
+        <v>3.8634615328027091</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="14"/>
+        <v>2.8655636589711779</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK8">
+        <v>0.79</v>
+      </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>0.875</v>
       </c>
       <c r="B9" s="1">
@@ -1022,10 +4040,57 @@
       <c r="W9">
         <v>1.3009999999999999</v>
       </c>
+      <c r="X9">
+        <f t="shared" si="6"/>
+        <v>2.0403492559742293</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" si="7"/>
+        <v>1.2969999999999999</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="8"/>
+        <v>0.22366666666666668</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="9"/>
+        <v>2.808988764044944</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="10"/>
+        <v>0.17371328907866612</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="11"/>
+        <v>3.2656456513414387</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="12"/>
+        <v>3.699928874038104</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="13"/>
+        <v>3.7319410885095472</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="14"/>
+        <v>2.6912767578593124</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK9">
+        <v>0.80500000000000005</v>
+      </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="B10" s="1">
@@ -1076,10 +4141,57 @@
       <c r="W10">
         <v>1.373</v>
       </c>
+      <c r="X10">
+        <f t="shared" si="6"/>
+        <v>2.0189206278062795</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="7"/>
+        <v>1.361</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="8"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="9"/>
+        <v>2.7472527472527473</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>0.19508028507622477</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>3.2229116593463214</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="12"/>
+        <v>3.6130722294987709</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="13"/>
+        <v>3.6004206442163853</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="14"/>
+        <v>2.6165738437701638</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK10">
+        <v>0.81100000000000005</v>
+      </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.125</v>
       </c>
       <c r="B11" s="1">
@@ -1130,10 +4242,57 @@
       <c r="W11">
         <v>1.49</v>
       </c>
+      <c r="X11">
+        <f t="shared" si="6"/>
+        <v>1.9466601075231034</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="7"/>
+        <v>1.47</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="8"/>
+        <v>0.23833333333333331</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="9"/>
+        <v>2.6178010471204187</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>0.26623044212388169</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>3.116186423774836</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="12"/>
+        <v>3.5155320869606586</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="13"/>
+        <v>3.4689001999232234</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="14"/>
+        <v>2.5287966187253934</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK11">
+        <v>0.81899999999999995</v>
+      </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.25</v>
       </c>
       <c r="B12" s="1">
@@ -1184,10 +4343,57 @@
       <c r="W12">
         <v>1.597</v>
       </c>
+      <c r="X12">
+        <f t="shared" si="6"/>
+        <v>1.9118969895966105</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" si="7"/>
+        <v>1.6053333333333335</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="8"/>
+        <v>0.24966666666666668</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="9"/>
+        <v>2.5380710659898478</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>0.32316570560177293</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>3.0592511602969448</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="12"/>
+        <v>3.3824168658987177</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="13"/>
+        <v>3.3373797556300615</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="14"/>
+        <v>2.3957319338085066</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK12">
+        <v>0.83199999999999996</v>
+      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.375</v>
       </c>
       <c r="B13" s="1">
@@ -1238,10 +4444,57 @@
       <c r="W13">
         <v>1.78</v>
       </c>
+      <c r="X13">
+        <f t="shared" si="6"/>
+        <v>1.8478408014078789</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" si="7"/>
+        <v>1.8406666666666667</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.26566666666666666</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="9"/>
+        <v>2.4096385542168677</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>0.36790442126263656</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>3.036881802466513</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="12"/>
+        <v>3.2208340130978312</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="13"/>
+        <v>3.2058593113368996</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="14"/>
+        <v>2.2254833373722382</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK13">
+        <v>0.85199999999999998</v>
+      </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="B14" s="1">
@@ -1292,10 +4545,57 @@
       <c r="W14">
         <v>1.9570000000000001</v>
       </c>
+      <c r="X14">
+        <f t="shared" si="6"/>
+        <v>1.809199411476679</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" si="7"/>
+        <v>2.0303333333333335</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" si="8"/>
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="9"/>
+        <v>2.3201856148491879</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>0.27969181431152368</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>3.036881802466513</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="12"/>
+        <v>3.036881802466513</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="13"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="14"/>
+        <v>2.0245477483236081</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK14">
+        <v>0.86699999999999999</v>
+      </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.625</v>
       </c>
       <c r="B15" s="1">
@@ -1346,10 +4646,57 @@
       <c r="W15">
         <v>2.1459999999999999</v>
       </c>
+      <c r="X15">
+        <f t="shared" si="6"/>
+        <v>1.7269992315364364</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" si="7"/>
+        <v>2.2536666666666667</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" si="8"/>
+        <v>0.29933333333333334</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="9"/>
+        <v>2.1929824561403506</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="10"/>
+        <v>0.49110562053948303</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="11"/>
+        <v>3.1425887055804926</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="12"/>
+        <v>2.8970358953107511</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="13"/>
+        <v>2.9428184227505758</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="14"/>
+        <v>1.8812326643207831</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK15">
+        <v>0.92200000000000004</v>
+      </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.75</v>
       </c>
       <c r="B16" s="1">
@@ -1400,10 +4747,57 @@
       <c r="W16">
         <v>2.58</v>
       </c>
+      <c r="X16">
+        <f t="shared" si="6"/>
+        <v>1.6615834286440461</v>
+      </c>
+      <c r="Y16" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7503333333333333</v>
+      </c>
+      <c r="Z16" s="1">
+        <f t="shared" si="8"/>
+        <v>0.33166666666666667</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="9"/>
+        <v>2.0491803278688523</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="10"/>
+        <v>0.57590538237994071</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="11"/>
+        <v>3.2273884674209503</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="12"/>
+        <v>2.6514830850410096</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="13"/>
+        <v>2.8112979784574139</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="14"/>
+        <v>1.5912093105945351</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK16">
+        <v>0.93</v>
+      </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="17"/>
         <v>1.875</v>
       </c>
       <c r="B17" s="1">
@@ -1454,8 +4848,55 @@
       <c r="W17">
         <v>3.11</v>
       </c>
+      <c r="X17">
+        <f t="shared" si="6"/>
+        <v>1.5652490444700597</v>
+      </c>
+      <c r="Y17" s="1">
+        <f t="shared" si="7"/>
+        <v>3.4603333333333333</v>
+      </c>
+      <c r="Z17" s="1">
+        <f t="shared" si="8"/>
+        <v>0.377</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="9"/>
+        <v>1.8867924528301885</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="10"/>
+        <v>3.0014381973935578E-2</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="11"/>
+        <v>2.4085519668119426</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="12"/>
+        <v>2.3635303938510392</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="13"/>
+        <v>2.679777534164252</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="14"/>
+        <v>1.2297275279619602</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK17">
+        <v>0.97199999999999998</v>
+      </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1.75</v>
       </c>
@@ -1507,8 +4948,55 @@
       <c r="W18">
         <v>3.0819999999999999</v>
       </c>
+      <c r="X18">
+        <f t="shared" si="6"/>
+        <v>1.5481945426749981</v>
+      </c>
+      <c r="Y18" s="1">
+        <f t="shared" si="7"/>
+        <v>3.4706666666666663</v>
+      </c>
+      <c r="Z18" s="1">
+        <f t="shared" si="8"/>
+        <v>0.375</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="9"/>
+        <v>1.8726591760299625</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="10"/>
+        <v>0.28050261675620902</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="11"/>
+        <v>2.6590402015942161</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="12"/>
+        <v>2.378537584838007</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="13"/>
+        <v>2.8112979784574139</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="14"/>
+        <v>1.1965936894049314</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK18">
+        <v>0.92</v>
+      </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f xml:space="preserve"> A18 - 1/8</f>
         <v>1.625</v>
@@ -1561,10 +5049,57 @@
       <c r="W19">
         <v>2.93</v>
       </c>
+      <c r="X19">
+        <f t="shared" si="6"/>
+        <v>1.6194873853978451</v>
+      </c>
+      <c r="Y19" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0533333333333332</v>
+      </c>
+      <c r="Z19" s="1">
+        <f t="shared" si="8"/>
+        <v>0.35133333333333333</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="9"/>
+        <v>1.9607843137254901</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="10"/>
+        <v>0.31641417112169279</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="11"/>
+        <v>2.6769959787769579</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="12"/>
+        <v>2.5187888932161115</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="13"/>
+        <v>2.9428184227505758</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="14"/>
+        <v>1.3504422998686068</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK19">
+        <v>0.92</v>
+      </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A32" si="7" xml:space="preserve"> A19 - 1/8</f>
+        <f t="shared" ref="A20:A32" si="18" xml:space="preserve"> A19 - 1/8</f>
         <v>1.5</v>
       </c>
       <c r="B20" s="1">
@@ -1615,10 +5150,57 @@
       <c r="W20">
         <v>2.5760000000000001</v>
       </c>
+      <c r="X20">
+        <f t="shared" si="6"/>
+        <v>1.6951345755693583</v>
+      </c>
+      <c r="Y20" s="1">
+        <f t="shared" si="7"/>
+        <v>2.658666666666667</v>
+      </c>
+      <c r="Z20" s="1">
+        <f t="shared" si="8"/>
+        <v>0.32753333333333334</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="9"/>
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="10"/>
+        <v>0.4043128472878692</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="11"/>
+        <v>2.6769959787769579</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="12"/>
+        <v>2.6769959787769579</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="13"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="14"/>
+        <v>1.5285673328556015</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK20">
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>1.375</v>
       </c>
       <c r="B21" s="1">
@@ -1669,10 +5251,57 @@
       <c r="W21">
         <v>2.2469999999999999</v>
       </c>
+      <c r="X21">
+        <f t="shared" si="6"/>
+        <v>1.7431459792244264</v>
+      </c>
+      <c r="Y21" s="1">
+        <f t="shared" si="7"/>
+        <v>2.2756666666666665</v>
+      </c>
+      <c r="Z21" s="1">
+        <f t="shared" si="8"/>
+        <v>0.30133333333333334</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="9"/>
+        <v>2.1881838074398248</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="10"/>
+        <v>0.4227779824965836</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="11"/>
+        <v>2.6677634111726007</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="12"/>
+        <v>2.8791524024208925</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="13"/>
+        <v>3.2058593113368996</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="14"/>
+        <v>1.7656791077660836</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK21">
+        <v>0.86</v>
+      </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>1.25</v>
       </c>
       <c r="B22" s="1">
@@ -1723,10 +5352,57 @@
       <c r="W22">
         <v>1.92</v>
       </c>
+      <c r="X22">
+        <f t="shared" si="6"/>
+        <v>1.8047480620155039</v>
+      </c>
+      <c r="Y22" s="1">
+        <f t="shared" si="7"/>
+        <v>1.9573333333333334</v>
+      </c>
+      <c r="Z22" s="1">
+        <f t="shared" si="8"/>
+        <v>0.27766666666666667</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="9"/>
+        <v>2.3255813953488373</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="10"/>
+        <v>0.42454779174151192</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="11"/>
+        <v>2.6659936019276724</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="12"/>
+        <v>3.0905413936691843</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="13"/>
+        <v>3.3373797556300615</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="14"/>
+        <v>2.0106724223405643</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK22">
+        <v>0.84599999999999997</v>
+      </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>1.125</v>
       </c>
       <c r="B23" s="1">
@@ -1777,10 +5453,57 @@
       <c r="W23">
         <v>1.6990000000000001</v>
       </c>
+      <c r="X23">
+        <f t="shared" si="6"/>
+        <v>1.9114184814596822</v>
+      </c>
+      <c r="Y23" s="1">
+        <f t="shared" si="7"/>
+        <v>1.7</v>
+      </c>
+      <c r="Z23" s="1">
+        <f t="shared" si="8"/>
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="9"/>
+        <v>2.5</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="10"/>
+        <v>0.28588270495428425</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="11"/>
+        <v>2.8739912321085139</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="12"/>
+        <v>3.3028152895399403</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="13"/>
+        <v>3.4689001999232234</v>
+      </c>
+      <c r="AG23">
+        <f t="shared" si="14"/>
+        <v>2.2525294285929851</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK23">
+        <v>0.82</v>
+      </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="B24" s="1">
@@ -1831,10 +5554,57 @@
       <c r="W24">
         <v>1.5629999999999999</v>
       </c>
+      <c r="X24">
+        <f t="shared" si="6"/>
+        <v>1.9917836818533861</v>
+      </c>
+      <c r="Y24" s="1">
+        <f t="shared" si="7"/>
+        <v>1.5589999999999999</v>
+      </c>
+      <c r="Z24" s="1">
+        <f t="shared" si="8"/>
+        <v>0.24466666666666667</v>
+      </c>
+      <c r="AA24">
+        <f t="shared" si="9"/>
+        <v>2.6315789473684212</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="10"/>
+        <v>0.29965303756694084</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="11"/>
+        <v>2.8464505668832008</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" si="12"/>
+        <v>3.4457566420170824</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="13"/>
+        <v>3.6004206442163853</v>
+      </c>
+      <c r="AG24">
+        <f t="shared" si="14"/>
+        <v>2.4008712893159219</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK24">
+        <v>0.82299999999999995</v>
+      </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.875</v>
       </c>
       <c r="B25" s="1">
@@ -1885,10 +5655,57 @@
       <c r="W25">
         <v>1.4770000000000001</v>
       </c>
+      <c r="X25">
+        <f t="shared" si="6"/>
+        <v>1.9614743570276338</v>
+      </c>
+      <c r="Y25" s="1">
+        <f t="shared" si="7"/>
+        <v>1.4490000000000001</v>
+      </c>
+      <c r="Z25" s="1">
+        <f t="shared" si="8"/>
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="9"/>
+        <v>2.6385224274406331</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="10"/>
+        <v>8.0763502960298439E-2</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="11"/>
+        <v>3.3936744033998067</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="12"/>
+        <v>3.5955831608005528</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="13"/>
+        <v>3.7319410885095472</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="14"/>
+        <v>2.5576594300423316</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK25">
+        <v>0.81499999999999995</v>
+      </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.75</v>
       </c>
       <c r="B26" s="1">
@@ -1939,10 +5756,57 @@
       <c r="W26">
         <v>1.36</v>
       </c>
+      <c r="X26">
+        <f t="shared" si="6"/>
+        <v>2.0347889848460161</v>
+      </c>
+      <c r="Y26" s="1">
+        <f t="shared" si="7"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="Z26" s="1">
+        <f t="shared" si="8"/>
+        <v>0.22799999999999998</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="9"/>
+        <v>2.770083102493075</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="10"/>
+        <v>0.3265370598434707</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="11"/>
+        <v>2.65635373275029</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="12"/>
+        <v>3.6359649122807021</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="13"/>
+        <v>3.8634615328027091</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="14"/>
+        <v>2.5733964810635515</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK26">
+        <v>0.80700000000000005</v>
+      </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.625</v>
       </c>
       <c r="B27" s="1">
@@ -1993,10 +5857,57 @@
       <c r="W27">
         <v>1.26</v>
       </c>
+      <c r="X27">
+        <f t="shared" si="6"/>
+        <v>2.1048999309868881</v>
+      </c>
+      <c r="Y27" s="1">
+        <f t="shared" si="7"/>
+        <v>1.236</v>
+      </c>
+      <c r="Z27" s="1">
+        <f t="shared" si="8"/>
+        <v>0.217</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="9"/>
+        <v>2.8985507246376816</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="10"/>
+        <v>0.36104254297723237</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="11"/>
+        <v>2.5355845417821241</v>
+      </c>
+      <c r="AE27">
+        <f t="shared" si="12"/>
+        <v>3.7992334422024374</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="13"/>
+        <v>3.994981977095871</v>
+      </c>
+      <c r="AG27">
+        <f t="shared" si="14"/>
+        <v>2.74771027631349</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK27">
+        <v>0.79900000000000004</v>
+      </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
       <c r="B28" s="1">
@@ -2047,10 +5958,57 @@
       <c r="W28">
         <v>1.2270000000000001</v>
       </c>
+      <c r="X28">
+        <f t="shared" si="6"/>
+        <v>2.1435839566364301</v>
+      </c>
+      <c r="Y28" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1966666666666665</v>
+      </c>
+      <c r="Z28" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20766666666666667</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="9"/>
+        <v>2.9585798816568047</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="10"/>
+        <v>0.1103498837274639</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="11"/>
+        <v>3.538355178781198</v>
+      </c>
+      <c r="AE28">
+        <f t="shared" si="12"/>
+        <v>3.9797547136910536</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="13"/>
+        <v>4.1265024213890324</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" si="14"/>
+        <v>2.9428811578427143</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK28">
+        <v>0.79700000000000004</v>
+      </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.375</v>
       </c>
       <c r="B29" s="1">
@@ -2101,10 +6059,57 @@
       <c r="W29">
         <v>1.2</v>
       </c>
+      <c r="X29">
+        <f t="shared" si="6"/>
+        <v>2.1969696969696968</v>
+      </c>
+      <c r="Y29" s="1">
+        <f t="shared" si="7"/>
+        <v>1.175</v>
+      </c>
+      <c r="Z29" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20466666666666666</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="9"/>
+        <v>3.0303030303030303</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="10"/>
+        <v>0.15377074007336411</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="11"/>
+        <v>3.3429613252246471</v>
+      </c>
+      <c r="AE29">
+        <f t="shared" si="12"/>
+        <v>4.0349296555547856</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="13"/>
+        <v>4.2580228656821948</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="14"/>
+        <v>2.9796391724058955</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK29">
+        <v>0.78800000000000003</v>
+      </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.25</v>
       </c>
       <c r="B30" s="1">
@@ -2155,10 +6160,57 @@
       <c r="W30">
         <v>1.19</v>
       </c>
+      <c r="X30">
+        <f t="shared" si="6"/>
+        <v>2.236586942469295</v>
+      </c>
+      <c r="Y30" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1583333333333334</v>
+      </c>
+      <c r="Z30" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20099999999999998</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="9"/>
+        <v>3.0769230769230766</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="10"/>
+        <v>0.22298795329986909</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="11"/>
+        <v>2.9968752590921222</v>
+      </c>
+      <c r="AE30">
+        <f t="shared" si="12"/>
+        <v>4.1118150255914676</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="13"/>
+        <v>4.3895433099753571</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="14"/>
+        <v>3.044271061999881</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK30">
+        <v>0.78300000000000003</v>
+      </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0.125</v>
       </c>
       <c r="B31" s="1">
@@ -2209,10 +6261,57 @@
       <c r="W31">
         <v>1.1830000000000001</v>
       </c>
+      <c r="X31">
+        <f t="shared" si="6"/>
+        <v>2.2894877006282841</v>
+      </c>
+      <c r="Y31" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1493333333333335</v>
+      </c>
+      <c r="Z31" s="1">
+        <f t="shared" si="8"/>
+        <v>0.19633333333333333</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="9"/>
+        <v>3.134796238244514</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="10"/>
+        <v>0.13867878993523419</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="11"/>
+        <v>3.4605756575976141</v>
+      </c>
+      <c r="AE31">
+        <f t="shared" si="12"/>
+        <v>4.2233090022414022</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="13"/>
+        <v>4.5210637542685186</v>
+      </c>
+      <c r="AG31">
+        <f t="shared" si="14"/>
+        <v>3.1528062869844575</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK31">
+        <v>0.77200000000000002</v>
+      </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="B32" s="1">
@@ -2257,8 +6356,56 @@
       <c r="W32">
         <v>1.17</v>
       </c>
+      <c r="X32" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y32" s="1">
+        <f t="shared" si="7"/>
+        <v>1.1366666666666667</v>
+      </c>
+      <c r="Z32" s="1">
+        <f t="shared" si="8"/>
+        <v>0.19333333333333336</v>
+      </c>
+      <c r="AA32" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC32" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD32" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE32">
+        <f t="shared" si="12"/>
+        <v>4.2926483972090193</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="13"/>
+        <v>4.65258419856168</v>
+      </c>
+      <c r="AG32">
+        <f t="shared" si="14"/>
+        <v>3.2087990417419645</v>
+      </c>
+      <c r="AH32">
+        <f t="shared" si="15"/>
+        <v>0.2630408885863238</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="16"/>
+        <v>3.0743388670437377</v>
+      </c>
+      <c r="AK32">
+        <v>0.76900000000000002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>